--- a/1-introduction/assets/mdp_race_car.xlsx
+++ b/1-introduction/assets/mdp_race_car.xlsx
@@ -12,13 +12,14 @@
     <sheet name="DP-Eval" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="DP-VI" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Convergence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Analytical" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MC-Episodes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="MC-VQ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TD0" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SARSA" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="QLearning" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Comparisons" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Analytical" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MC-Episodes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="MC-VQ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="TD0" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SARSA" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="QLearning" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,13 +127,35 @@
       <sz val="12"/>
     </font>
     <font>
-      <i val="1"/>
-      <sz val="10"/>
+      <name val="Courier New"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00375623"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -201,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -292,7 +315,41 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -306,8 +363,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -680,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -2068,17 +2124,17 @@
       </c>
       <c r="B106" s="21" t="inlineStr">
         <is>
-          <t>Analytical</t>
+          <t>Comparisons</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Algebra</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Solves the Bellman equation EXACTLY by hand: sets up system of equations, shows circular dependency, substitutes, and solves for V*.</t>
+          <t>Side-by-side comparison: DP-Eval vs DP-VI (expectation vs max), DP-VI vs Q-Learning (model-based vs model-free), and all 5 methods.</t>
         </is>
       </c>
       <c r="E106" s="9" t="n"/>
@@ -2086,7 +2142,7 @@
       <c r="G106" s="9" t="n"/>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>Closed-form V*, Q* with step-by-step derivation</t>
+          <t>Where P(s'|s,a) appears and why methods differ</t>
         </is>
       </c>
       <c r="I106" s="9" t="n"/>
@@ -2100,17 +2156,17 @@
       </c>
       <c r="B107" s="21" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Analytical</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>All Methods</t>
+          <t>Algebra</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Collects V^pi, V*, Q^pi, Q* for all policies in one place. Demonstrates Policy Iteration: evaluate -&gt; improve -&gt; converge.</t>
+          <t>Solves the Bellman equation EXACTLY by hand: sets up system of equations, shows circular dependency, substitutes, and solves for V*.</t>
         </is>
       </c>
       <c r="E107" s="9" t="n"/>
@@ -2118,7 +2174,7 @@
       <c r="G107" s="9" t="n"/>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>Complete V/Q tables + policy iteration demo</t>
+          <t>Closed-form V*, Q* with step-by-step derivation</t>
         </is>
       </c>
       <c r="I107" s="9" t="n"/>
@@ -2132,17 +2188,17 @@
       </c>
       <c r="B108" s="21" t="inlineStr">
         <is>
-          <t>MC-Episodes</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Monte Carlo</t>
+          <t>All Methods</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Simulates 5 episodes following an epsilon-greedy optimal policy. Computes return G_t backward for each step.</t>
+          <t>Collects V^pi, V*, Q^pi, Q* for all policies in one place. Demonstrates Policy Iteration: evaluate -&gt; improve -&gt; converge.</t>
         </is>
       </c>
       <c r="E108" s="9" t="n"/>
@@ -2150,7 +2206,7 @@
       <c r="G108" s="9" t="n"/>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>Episode trajectories with discounted returns</t>
+          <t>Complete V/Q tables + policy iteration demo</t>
         </is>
       </c>
       <c r="I108" s="9" t="n"/>
@@ -2164,7 +2220,7 @@
       </c>
       <c r="B109" s="21" t="inlineStr">
         <is>
-          <t>MC-VQ</t>
+          <t>MC-Episodes</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -2174,7 +2230,7 @@
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>First-visit MC estimation: averages G_t returns across episodes to estimate V^MC(s) and Q^MC(s,a).</t>
+          <t>Simulates 5 episodes following an epsilon-greedy optimal policy. Computes return G_t backward for each step.</t>
         </is>
       </c>
       <c r="E109" s="9" t="n"/>
@@ -2182,7 +2238,7 @@
       <c r="G109" s="9" t="n"/>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>V^MC, Q^MC, greedy policy from MC</t>
+          <t>Episode trajectories with discounted returns</t>
         </is>
       </c>
       <c r="I109" s="9" t="n"/>
@@ -2196,17 +2252,17 @@
       </c>
       <c r="B110" s="21" t="inlineStr">
         <is>
-          <t>TD0</t>
+          <t>MC-VQ</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Temporal Difference</t>
+          <t>Monte Carlo</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>TD(0) updates V(s) after EVERY transition using V(s) &lt;- V(s) + alpha*[r + gamma*V(s') - V(s)]. Step-by-step trace.</t>
+          <t>First-visit MC estimation: averages G_t returns across episodes to estimate V^MC(s) and Q^MC(s,a).</t>
         </is>
       </c>
       <c r="E110" s="9" t="n"/>
@@ -2214,7 +2270,7 @@
       <c r="G110" s="9" t="n"/>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>V^TD(s) after all episodes</t>
+          <t>V^MC, Q^MC, greedy policy from MC</t>
         </is>
       </c>
       <c r="I110" s="9" t="n"/>
@@ -2228,7 +2284,7 @@
       </c>
       <c r="B111" s="21" t="inlineStr">
         <is>
-          <t>SARSA</t>
+          <t>TD0</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
@@ -2238,7 +2294,7 @@
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>On-policy Q-learning: Q(s,a) &lt;- Q(s,a) + alpha*[r + gamma*Q(s',a') - Q(s,a)]. Uses the ACTUAL next action a'.</t>
+          <t>TD(0) updates V(s) after EVERY transition using V(s) &lt;- V(s) + alpha*[r + gamma*V(s') - V(s)]. Step-by-step trace.</t>
         </is>
       </c>
       <c r="E111" s="9" t="n"/>
@@ -2246,7 +2302,7 @@
       <c r="G111" s="9" t="n"/>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>Q^SARSA(s,a) + greedy policy</t>
+          <t>V^TD(s) after all episodes</t>
         </is>
       </c>
       <c r="I111" s="9" t="n"/>
@@ -2260,7 +2316,7 @@
       </c>
       <c r="B112" s="21" t="inlineStr">
         <is>
-          <t>QLearning</t>
+          <t>SARSA</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -2270,7 +2326,7 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Off-policy Q-learning: Q(s,a) &lt;- Q(s,a) + alpha*[r + gamma*max Q(s',.) - Q(s,a)]. Uses the BEST next action.</t>
+          <t>On-policy Q-learning: Q(s,a) &lt;- Q(s,a) + alpha*[r + gamma*Q(s',a') - Q(s,a)]. Uses the ACTUAL next action a'.</t>
         </is>
       </c>
       <c r="E112" s="9" t="n"/>
@@ -2278,220 +2334,251 @@
       <c r="G112" s="9" t="n"/>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>Q*(s,a) estimate + optimal policy</t>
+          <t>Q^SARSA(s,a) + greedy policy</t>
         </is>
       </c>
       <c r="I112" s="9" t="n"/>
       <c r="J112" s="9" t="n"/>
     </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>QLearning</t>
+        </is>
+      </c>
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>Temporal Difference</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="inlineStr">
+        <is>
+          <t>Off-policy Q-learning: Q(s,a) &lt;- Q(s,a) + alpha*[r + gamma*max Q(s',.) - Q(s,a)]. Uses the BEST next action.</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+      <c r="H113" s="9" t="inlineStr">
+        <is>
+          <t>Q*(s,a) estimate + optimal policy</t>
+        </is>
+      </c>
+      <c r="I113" s="9" t="n"/>
+      <c r="J113" s="9" t="n"/>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>9. The Big Picture: From Problem to Solution</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>DEFINE the MDP (Problem sheet)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      |</t>
+          <t>DEFINE the MDP (Problem sheet)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      v</t>
+          <t xml:space="preserve">      |</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>SOLVE for V* and pi* --- three paths:</t>
+          <t xml:space="preserve">      v</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      |                   |                    |</t>
+          <t>SOLVE for V* and pi* --- three paths:</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  [MODEL-BASED]      [MODEL-FREE]         [MODEL-FREE]</t>
+          <t xml:space="preserve">      |                   |                    |</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dynamic Prog.      Monte Carlo            TD Learning</t>
+          <t xml:space="preserve">  [MODEL-BASED]      [MODEL-FREE]         [MODEL-FREE]</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (DP-Eval, DP-VI)   (MC-Episodes, MC-VQ)  (TD0, SARSA, QLearning)</t>
+          <t xml:space="preserve">  Dynamic Prog.      Monte Carlo            TD Learning</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs: P, R        Needs: episodes        Needs: single transitions</t>
+          <t xml:space="preserve">  (DP-Eval, DP-VI)   (MC-Episodes, MC-VQ)  (TD0, SARSA, QLearning)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Exact (converges)  Unbiased, high var.    Biased, low variance</t>
+          <t xml:space="preserve">  Needs: P, R        Needs: episodes        Needs: single transitions</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      |                   |                    |</t>
+          <t xml:space="preserve">  Exact (converges)  Unbiased, high var.    Biased, low variance</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">      +-------------------+--------------------+</t>
+          <t xml:space="preserve">      |                   |                    |</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                          |</t>
+          <t xml:space="preserve">      +-------------------+--------------------+</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">                          v</t>
+          <t xml:space="preserve">                          |</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>VERIFY: all methods converge to the SAME answer: pi*(Cool)=Fast, pi*(Warm)=Slow</t>
+          <t xml:space="preserve">                          v</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
+          <t>VERIFY: all methods converge to the SAME answer: pi*(Cool)=Fast, pi*(Warm)=Slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">        (Analytical sheet proves it algebraically; Convergence sheet shows DP getting there)</t>
         </is>
       </c>
     </row>
-    <row r="131"/>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Color Legend Used Throughout This Workbook</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="22" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="22" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B133" s="23" t="inlineStr">
+      <c r="B134" s="23" t="inlineStr">
         <is>
           <t>Orange cells = LIVE FORMULA (click cell -&gt; formula bar shows computation)</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="24" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="24" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B134" s="23" t="inlineStr">
+      <c r="B135" s="23" t="inlineStr">
         <is>
           <t>Red cells = Terminal state / penalty</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="25" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="25" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B135" s="23" t="inlineStr">
+      <c r="B136" s="23" t="inlineStr">
         <is>
           <t>Green cells = Positive reward</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="26" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="26" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B136" s="23" t="inlineStr">
+      <c r="B137" s="23" t="inlineStr">
         <is>
           <t>Light green cells = Best Q-value or solution</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="27" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="27" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B137" s="23" t="inlineStr">
+      <c r="B138" s="23" t="inlineStr">
         <is>
           <t>Blue cells = Episode headers</t>
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="28" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="28" t="inlineStr">
         <is>
           <t>  </t>
         </is>
       </c>
-      <c r="B138" s="23" t="inlineStr">
+      <c r="B139" s="23" t="inlineStr">
         <is>
           <t>Light blue cells = Initialization / sub-headers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="148">
+  <mergeCells count="150">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="H110:J110"/>
     <mergeCell ref="H109:J109"/>
-    <mergeCell ref="A115:J115"/>
     <mergeCell ref="D110:G110"/>
     <mergeCell ref="D60:G60"/>
     <mergeCell ref="A130:J130"/>
@@ -2529,6 +2616,7 @@
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A81:J81"/>
     <mergeCell ref="A121:J121"/>
+    <mergeCell ref="D113:G113"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A67:J67"/>
@@ -2577,7 +2665,6 @@
     <mergeCell ref="H105:J105"/>
     <mergeCell ref="D63:G63"/>
     <mergeCell ref="A79:J79"/>
-    <mergeCell ref="B133:J133"/>
     <mergeCell ref="H107:J107"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="D105:G105"/>
@@ -2591,6 +2678,7 @@
     <mergeCell ref="A74:J74"/>
     <mergeCell ref="H102:J102"/>
     <mergeCell ref="A27:J27"/>
+    <mergeCell ref="H113:J113"/>
     <mergeCell ref="C37:G37"/>
     <mergeCell ref="H34:J34"/>
     <mergeCell ref="C51:F51"/>
@@ -2603,6 +2691,7 @@
     <mergeCell ref="B136:J136"/>
     <mergeCell ref="H36:J36"/>
     <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A131:J131"/>
     <mergeCell ref="A126:J126"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="G54:J54"/>
@@ -2616,6 +2705,7 @@
     <mergeCell ref="H37:J37"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="G52:J52"/>
+    <mergeCell ref="B139:J139"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="D111:G111"/>
     <mergeCell ref="H62:J62"/>
@@ -2645,6 +2735,376 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monte Carlo — First-Visit V(s) and Q(s,a) Estimation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Each cell = G_t of the first visit in that episode (cross-sheet ref).  V/Q = AVERAGE of those returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V^MC(s) = average of first-visit G_t per state</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Ep1 G_t ✱</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Ep2 G_t ✱</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Ep3 G_t ✱</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Ep4 G_t ✱</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Ep5 G_t ✱</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>V^MC(s) ✱</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Cool</t>
+        </is>
+      </c>
+      <c r="B6" s="29">
+        <f>'MC-Episodes'!G7</f>
+        <v/>
+      </c>
+      <c r="C6" s="29">
+        <f>'MC-Episodes'!G31</f>
+        <v/>
+      </c>
+      <c r="D6" s="29">
+        <f>'MC-Episodes'!G55</f>
+        <v/>
+      </c>
+      <c r="E6" s="29">
+        <f>'MC-Episodes'!G79</f>
+        <v/>
+      </c>
+      <c r="F6" s="29">
+        <f>'MC-Episodes'!G97</f>
+        <v/>
+      </c>
+      <c r="G6" s="29">
+        <f>AVERAGE(B6:F6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="B7" s="29">
+        <f>'MC-Episodes'!G15</f>
+        <v/>
+      </c>
+      <c r="C7" s="29">
+        <f>'MC-Episodes'!G32</f>
+        <v/>
+      </c>
+      <c r="D7" s="29">
+        <f>'MC-Episodes'!G56</f>
+        <v/>
+      </c>
+      <c r="E7" s="29">
+        <f>'MC-Episodes'!G81</f>
+        <v/>
+      </c>
+      <c r="F7" s="29">
+        <f>'MC-Episodes'!G98</f>
+        <v/>
+      </c>
+      <c r="G7" s="29">
+        <f>AVERAGE(B7:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="53" t="inlineStr">
+        <is>
+          <t>Overheated</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="20" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q^MC(s,a) = average of first-visit G_t per (s,a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>(s, a)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Ep1 G_t ✱</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Ep2 G_t ✱</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Ep3 G_t ✱</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Ep4 G_t ✱</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Ep5 G_t ✱</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Q^MC(s,a) ✱</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>(Cool, Slow)</t>
+        </is>
+      </c>
+      <c r="B12" s="29">
+        <f>'MC-Episodes'!G20</f>
+        <v/>
+      </c>
+      <c r="C12" s="29">
+        <f>'MC-Episodes'!G49</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>'MC-Episodes'!G73</f>
+        <v/>
+      </c>
+      <c r="G12" s="29">
+        <f>AVERAGE(B12:F12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>(Cool, Fast)</t>
+        </is>
+      </c>
+      <c r="B13" s="29">
+        <f>'MC-Episodes'!G7</f>
+        <v/>
+      </c>
+      <c r="C13" s="29">
+        <f>'MC-Episodes'!G31</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>'MC-Episodes'!G55</f>
+        <v/>
+      </c>
+      <c r="E13" s="29">
+        <f>'MC-Episodes'!G79</f>
+        <v/>
+      </c>
+      <c r="F13" s="29">
+        <f>'MC-Episodes'!G97</f>
+        <v/>
+      </c>
+      <c r="G13" s="29">
+        <f>AVERAGE(B13:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>(Warm, Slow)</t>
+        </is>
+      </c>
+      <c r="B14" s="29">
+        <f>'MC-Episodes'!G15</f>
+        <v/>
+      </c>
+      <c r="C14" s="29">
+        <f>'MC-Episodes'!G32</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>'MC-Episodes'!G56</f>
+        <v/>
+      </c>
+      <c r="E14" s="29">
+        <f>'MC-Episodes'!G81</f>
+        <v/>
+      </c>
+      <c r="G14" s="29">
+        <f>AVERAGE(B14:F14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>(Warm, Fast)</t>
+        </is>
+      </c>
+      <c r="D15" s="29">
+        <f>'MC-Episodes'!G74</f>
+        <v/>
+      </c>
+      <c r="E15" s="29">
+        <f>'MC-Episodes'!G92</f>
+        <v/>
+      </c>
+      <c r="F15" s="29">
+        <f>'MC-Episodes'!G98</f>
+        <v/>
+      </c>
+      <c r="G15" s="29">
+        <f>AVERAGE(B15:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Greedy Policy from Q^MC: π(s) = argmax_a Q^MC(s,a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>π(s) ✱</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Q^MC(s,π(s)) ✱</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Cool</t>
+        </is>
+      </c>
+      <c r="B19" s="29">
+        <f>IF(G13&gt;=G12,"Fast","Slow")</f>
+        <v/>
+      </c>
+      <c r="C19" s="29">
+        <f>MAX(G12,G13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="B20" s="29">
+        <f>IF(G15&gt;=G14,"Fast","Slow")</f>
+        <v/>
+      </c>
+      <c r="C20" s="29">
+        <f>MAX(G14,G15)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2788,10 +3248,10 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="48" t="n">
+      <c r="L6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6961,7 +7421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7133,16 +7593,16 @@
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
-      <c r="M6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="48" t="n">
+      <c r="M6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12358,7 +12818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12519,16 +12979,16 @@
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="48" t="n">
+      <c r="L6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -34523,6 +34983,1551 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="47" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method Comparisons: DP-Eval vs DP-VI vs Model-Free Methods</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Part 1: DP-Eval (Policy Evaluation) vs DP-VI (Value Iteration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Both are Dynamic Programming methods that sweep over ALL states using the KNOWN model. The difference is the OPERATOR: expectation vs max.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>DP-Eval (Policy Evaluation)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Question it answers</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>How good is THIS specific policy pi?</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>What is the BEST possible policy?</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n"/>
+      <c r="I7" s="9" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Bellman equation used</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Expectation: V(s) = SUM P*[R + gamma*V(s')]  under FIXED pi</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Optimality: V(s) = MAX_a SUM P*[R + gamma*V(s')]  over ALL actions</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Key operator</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>NONE (just follow the given policy)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>MAX over actions (find the best one)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Input required</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>A specific policy (e.g. 'always slow')</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>No policy needed — finds optimal automatically</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>V^pi(s) for that one policy</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>V*(s), Q*(s,a), and pi*(s) — all optimal</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Columns in the sheet</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>V_k(Cool), V_k(Warm), |DV|  (no Q columns)</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Q(s,Slow), Q(s,Fast), V*=MAX(Q), pi*=argmax(Q), |DV|</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="n"/>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Number of runs needed</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>One per policy (4 policies = 4 blocks)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>One run finds everything</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Uses transition probs P?</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>YES — embedded in the formula</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>YES — embedded in the formula</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="n"/>
+      <c r="I14" s="9" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Convergence target</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Different for each policy (Cautious-&gt;10, Optimal-&gt;15.5)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Always V*: V*(Cool)=15.5, V*(Warm)=14.5</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Formula Comparison — Same (Cool, Slow) transition, different equations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>DP-Eval
+(Cautious: always Slow)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>V_{k+1}(Cool) = 0.5*(1+0.9*V_k(C)) + 0.5*(1+0.9*V_k(W))</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Policy says Slow, so we ONLY compute the Slow outcome. No choice involved — just evaluate what this policy gives us.</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>DP-Eval
+(Optimal: Fast@Cool)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>V_{k+1}(Cool) = 0.5*(2+0.9*V_k(C)) + 0.5*(2+0.9*V_k(W))</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Policy says Fast at Cool, so we compute the Fast outcome. Still no MAX — policy is fixed.</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>DP-VI</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>V_{k+1}(Cool) = MAX( 0.5*(1+0.9*V_k(C))+0.5*(1+0.9*V_k(W)),  0.5*(2+0.9*V_k(C))+0.5*(2+0.9*V_k(W)) )</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Computes BOTH Slow and Fast Q-values, then takes MAX. This IS how it finds the optimal policy — it tries everything.</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="n"/>
+      <c r="I21" s="9" t="n"/>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>How DP-Eval and DP-VI relate (Policy Iteration uses BOTH):</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>1. START with any policy (e.g. Cautious: always Slow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>2. EVALUATE it using DP-Eval -&gt; get V^cautious(Cool)=10, V^cautious(Warm)=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>3. IMPROVE: for each state, compute Q^cautious(s,a) for all actions, pick argmax -&gt; new policy = Fast@Cool, Slow@Warm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="38" t="inlineStr">
+        <is>
+          <t>4. EVALUATE the new policy using DP-Eval -&gt; get V^optimal(Cool)=15.5, V^optimal(Warm)=14.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="38" t="inlineStr">
+        <is>
+          <t>5. IMPROVE: argmax Q^optimal -&gt; same policy (Fast@Cool, Slow@Warm) -&gt; CONVERGED!</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="38" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>DP-VI is a shortcut: it combines evaluate+improve into one step by using MAX directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>Instead of evaluating a policy fully then improving, it improves greedily at EVERY sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Live Proof: DP-Eval converged values vs DP-VI converged values</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>DP-Eval (Cautious)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>DP-Eval (Optimal)</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>DP-VI</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Eval-Opt = VI?</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>V(Cool)</t>
+        </is>
+      </c>
+      <c r="B35" s="29">
+        <f>'DP-Eval'!B59</f>
+        <v/>
+      </c>
+      <c r="C35" s="29">
+        <f>'DP-Eval'!B116</f>
+        <v/>
+      </c>
+      <c r="D35" s="29">
+        <f>'DP-VI'!D58</f>
+        <v/>
+      </c>
+      <c r="E35" s="29">
+        <f>IF(ABS(C35-D35)&lt;0.001,"YES — same V*","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>V(Warm)</t>
+        </is>
+      </c>
+      <c r="B36" s="29">
+        <f>'DP-Eval'!C59</f>
+        <v/>
+      </c>
+      <c r="C36" s="29">
+        <f>'DP-Eval'!C116</f>
+        <v/>
+      </c>
+      <c r="D36" s="29">
+        <f>'DP-VI'!G58</f>
+        <v/>
+      </c>
+      <c r="E36" s="29">
+        <f>IF(ABS(C36-D36)&lt;0.001,"YES — same V*","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>DP-Eval(Cautious) = 10: the cautious policy is suboptimal.  DP-Eval(Optimal) = DP-VI = 15.5/14.5: evaluating the optimal policy gives V*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Part 2: DP-VI (Model-Based) vs Q-Learning (Model-Free)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Both find Q* and pi*. The fundamental difference: DP-VI CALCULATES expectations using known P(s'|s,a). Q-Learning ESTIMATES them from samples.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Aspect</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>DP-VI (Model-Based)</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Knows P(s'|s,a)?</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>YES — hardcoded in the formula as 0.5, 0.5, 1.0, etc.</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>NO — never sees transition probabilities</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Knows R(s,a,s')?</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>YES — hardcoded as +1, +2, -10</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>NO — only observes the reward r after each transition</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>How it sees next states</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Sums over ALL possible s' simultaneously</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Observes ONE random s' per step (whatever happened)</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="J47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Update formula</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Q(s,a) = SUM_{s'} P(s'|s,a)*[R + gamma*max Q(s',*)]</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Q(s,a) &lt;- Q(s,a) + alpha*[r + gamma*max Q(s',*) - Q(s,a)]</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Learning rate alpha</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>alpha = 1 (replace with exact target)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>alpha = 0.1 (inch toward noisy target)</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="J49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Coverage per step</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>One SWEEP updates ALL (state, action) pairs</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>One step updates ONE (state, action) pair</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Convergence speed</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Fast: ~50 sweeps (deterministic)</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Slow: needs many episodes (stochastic)</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="J51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>When to use</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>When you KNOW the model (game rules, physics equations)</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>When you DON'T know the model (real world, complex simulations)</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>WHERE the transition probability P appears (and doesn't):</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>This is THE critical difference. Look at Q(Cool, Fast) computed both ways:</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="40" t="inlineStr">
+        <is>
+          <t>DP-VI formula:</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>Q(Cool,Fast) = 0.5 * (2 + 0.9*V(C))  +  0.5 * (2 + 0.9*V(W))</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 ^^^                     ^^^</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            P(Cool|Cool,Fast)=0.5    P(Warm|Cool,Fast)=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>Q-Learning step:</t>
+        </is>
+      </c>
+      <c r="B61" s="45" t="inlineStr">
+        <is>
+          <t>Agent picks Fast in Cool -&gt; lands in Warm (random), gets r=2</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="J61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>target = 2 + 0.9 * max(Q(Warm,Slow), Q(Warm,Fast))</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>Q(Cool,Fast) &lt;- Q(Cool,Fast) + 0.1 * (target - Q(Cool,Fast))</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ^^^ NO 0.5 anywhere! Only saw ONE outcome (Warm). Next time might be Cool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>How Q-Learning recovers P without knowing it:</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Visit 1: Fast in Cool -&gt; lands in Warm (r=2).   Q updated toward (2 + 0.9*max Q(Warm,.))</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Visit 2: Fast in Cool -&gt; lands in Cool (r=2).   Q updated toward (2 + 0.9*max Q(Cool,.))</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>Visit 3: Fast in Cool -&gt; lands in Warm (r=2).   Q updated toward (2 + 0.9*max Q(Warm,.))</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Visit 4: Fast in Cool -&gt; lands in Cool (r=2).   Q updated toward (2 + 0.9*max Q(Cool,.))</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="47" t="inlineStr">
+        <is>
+          <t>After many visits: ~50% landed in Cool, ~50% landed in Warm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="47" t="inlineStr">
+        <is>
+          <t>The running average of targets CONVERGES to: 0.5*(2+0.9*V(C)) + 0.5*(2+0.9*V(W))</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="47" t="inlineStr">
+        <is>
+          <t>...which is EXACTLY the DP-VI formula! The probabilities emerge from sampling frequency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Live Proof: DP-VI vs Q-Learning converged Q-values</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Q-Learning has only 5 episodes (76 steps) so it hasn't fully converged yet. With more episodes it would approach DP-VI exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Q(s,a)</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>DP-VI (exact)</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Q-Learning (5 eps)</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Converging?</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Q(Cool, Slow)</t>
+        </is>
+      </c>
+      <c r="B79" s="29">
+        <f>'DP-VI'!B58</f>
+        <v/>
+      </c>
+      <c r="C79" s="29">
+        <f>'QLearning'!B86</f>
+        <v/>
+      </c>
+      <c r="D79" s="29">
+        <f>ABS(B79-C79)</f>
+        <v/>
+      </c>
+      <c r="E79" s="29">
+        <f>IF(D79&lt;1,"Close","Far")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Q(Cool, Fast)</t>
+        </is>
+      </c>
+      <c r="B80" s="29">
+        <f>'DP-VI'!C58</f>
+        <v/>
+      </c>
+      <c r="C80" s="29">
+        <f>'QLearning'!C86</f>
+        <v/>
+      </c>
+      <c r="D80" s="29">
+        <f>ABS(B80-C80)</f>
+        <v/>
+      </c>
+      <c r="E80" s="29">
+        <f>IF(D80&lt;1,"Close","Far")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Q(Warm, Slow)</t>
+        </is>
+      </c>
+      <c r="B81" s="29">
+        <f>'DP-VI'!E58</f>
+        <v/>
+      </c>
+      <c r="C81" s="29">
+        <f>'QLearning'!B87</f>
+        <v/>
+      </c>
+      <c r="D81" s="29">
+        <f>ABS(B81-C81)</f>
+        <v/>
+      </c>
+      <c r="E81" s="29">
+        <f>IF(D81&lt;1,"Close","Far")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Q(Warm, Fast)</t>
+        </is>
+      </c>
+      <c r="B82" s="29">
+        <f>'DP-VI'!F58</f>
+        <v/>
+      </c>
+      <c r="C82" s="29">
+        <f>'QLearning'!C87</f>
+        <v/>
+      </c>
+      <c r="D82" s="29">
+        <f>ABS(B82-C82)</f>
+        <v/>
+      </c>
+      <c r="E82" s="29">
+        <f>IF(D82&lt;1,"Close","Far")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="48" t="inlineStr">
+        <is>
+          <t>Part 3: Complete Comparison — All Five Methods in This Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Every method converges to the same V* and pi*. They differ in what information they need and how they use it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>DP-Eval</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>DP-VI</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>SARSA</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>Q-Learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>Model-based</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>Model-based</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Model-free</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Model-free</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Model-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Finds V* or V^pi?</t>
+        </is>
+      </c>
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>V^pi only</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>V* (optimal)</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>V^pi estimate</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Q^pi estimate</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Q* estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Uses P(s'|s,a)?</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Uses R(s,a,s')?</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>NO (observes r)</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>NO (observes r)</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>NO (observes r)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>Policy needed?</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>YES (fixed pi)</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>NO (finds pi*)</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>YES (behavior)</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>YES (epsilon-greedy)</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>NO (off-policy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Update unit</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>Full sweep</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>Full sweep</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="inlineStr">
+        <is>
+          <t>Full episode</t>
+        </is>
+      </c>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>Single step</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Single step</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>1 (exact)</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>1 (exact)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>1/N (average)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>0.1 (small)</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>0.1 (small)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Bellman eq.</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Expectation</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>Optimality</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="inlineStr">
+        <is>
+          <t>None (returns)</t>
+        </is>
+      </c>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>Expectation</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Optimality</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>On/Off-policy</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="inlineStr">
+        <is>
+          <t>On-policy</t>
+        </is>
+      </c>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>On-policy</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Off-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>DP-Eval</t>
+        </is>
+      </c>
+      <c r="C98" s="9" t="inlineStr">
+        <is>
+          <t>DP-VI</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>MC-Episodes/VQ</t>
+        </is>
+      </c>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>SARSA</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>QLearning</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="39" t="inlineStr">
+        <is>
+          <t>KEY INSIGHT: The 0.5 in DP-VI's formula IS the transition probability. Q-Learning doesn't have it —</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="49" t="inlineStr">
+        <is>
+          <t>it recovers the same weighted average by visiting each outcome enough times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="49" t="inlineStr">
+        <is>
+          <t>DP-VI = analytical weighted sum.  Q-Learning = empirical running average.  Same destination, different roads.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="79">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A73:K73"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="G13:K13"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A101:K101"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B62:K62"/>
+    <mergeCell ref="B59:K59"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A71:K71"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A100:K100"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A68:K68"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B63:K63"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="G45:K45"/>
+    <mergeCell ref="B61:K61"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="A67:K67"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="B64:K64"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="A55:K55"/>
+    <mergeCell ref="B58:K58"/>
+    <mergeCell ref="A86:K86"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B57:K57"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="A31:K31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -34953,21 +36958,21 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38" t="inlineStr">
+      <c r="A38" s="50" t="inlineStr">
         <is>
           <t>1. ALGEBRA (this sheet): Introduce variable x, substitute, solve the resulting equation. Works for small MDPs.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
+      <c r="A39" s="50" t="inlineStr">
         <is>
           <t>2. LINEAR ALGEBRA: Write as matrix equation V = R + gamma*P*V, solve (I - gamma*P)*V = R. Works for any size.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38" t="inlineStr">
+      <c r="A40" s="50" t="inlineStr">
         <is>
           <t>3. ITERATIVE (DP): Start with V=0, repeatedly apply Bellman update. Converges to the fixed point (see DP-VI sheet).</t>
         </is>
@@ -34990,35 +36995,35 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38" t="inlineStr">
+      <c r="A45" s="50" t="inlineStr">
         <is>
           <t>Q*(Cool,Slow) = Q*(Warm,Slow) — same formula because both have 0.5/0.5 to Cool/Warm with R=1</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38" t="inlineStr">
+      <c r="A46" s="50" t="inlineStr">
         <is>
           <t>Q*(Cool,Fast) = Q*(Cool,Slow) + 1 — Fast just adds +1 more reward per transition (2 vs 1)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38" t="inlineStr">
+      <c r="A47" s="50" t="inlineStr">
         <is>
           <t>Q*(Warm,Fast) = -10 — no unknowns, Warm+Fast always goes to terminal Overheated</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38" t="inlineStr">
+      <c r="A48" s="50" t="inlineStr">
         <is>
           <t>Since Q*(Cool,Fast) &gt; Q*(Cool,Slow) always: V*(Cool) = Q*(Cool,Fast) — optimal action at Cool is Fast</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38" t="inlineStr">
+      <c r="A49" s="50" t="inlineStr">
         <is>
           <t>Since Q*(Warm,Slow) &gt;&gt; Q*(Warm,Fast)=-10: V*(Warm) = Q*(Warm,Slow) — optimal action at Warm is Slow</t>
         </is>
@@ -35309,7 +37314,7 @@
           <t>x = V*(Warm) =</t>
         </is>
       </c>
-      <c r="B71" s="39" t="n">
+      <c r="B71" s="51" t="n">
         <v>14.5</v>
       </c>
     </row>
@@ -35319,7 +37324,7 @@
           <t>V*(Cool) = x+1 =</t>
         </is>
       </c>
-      <c r="B72" s="39">
+      <c r="B72" s="51">
         <f>B71+1</f>
         <v/>
       </c>
@@ -35330,7 +37335,7 @@
           <t>V*(Overheated) =</t>
         </is>
       </c>
-      <c r="B73" s="40" t="n">
+      <c r="B73" s="52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -35594,15 +37599,15 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="41" t="inlineStr">
+      <c r="A93" s="53" t="inlineStr">
         <is>
           <t>Overheated</t>
         </is>
       </c>
-      <c r="B93" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="42" t="n">
+      <c r="B93" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="54" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="20">
@@ -35693,7 +37698,7 @@
           <t>V^cautious(Cool) = V^cautious(Warm) =</t>
         </is>
       </c>
-      <c r="B104" s="43" t="n">
+      <c r="B104" s="55" t="n">
         <v>10</v>
       </c>
     </row>
@@ -35854,7 +37859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35980,7 +37985,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="53" t="inlineStr">
         <is>
           <t>Overheated</t>
         </is>
@@ -36287,7 +38292,7 @@
     </row>
     <row r="41"/>
     <row r="42">
-      <c r="A42" s="44" t="inlineStr">
+      <c r="A42" s="48" t="inlineStr">
         <is>
           <t>Section 2e: Q*(s,a) from V*</t>
         </is>
@@ -36555,7 +38560,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="41" t="inlineStr">
+      <c r="A65" s="53" t="inlineStr">
         <is>
           <t>Overheated</t>
         </is>
@@ -36584,7 +38589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36625,17 +38630,17 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>Episode 1</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="46" t="n"/>
-      <c r="F5" s="46" t="n"/>
-      <c r="G5" s="46" t="n"/>
+      <c r="B5" s="57" t="n"/>
+      <c r="C5" s="57" t="n"/>
+      <c r="D5" s="57" t="n"/>
+      <c r="E5" s="57" t="n"/>
+      <c r="F5" s="57" t="n"/>
+      <c r="G5" s="57" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -37295,7 +39300,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="47" t="inlineStr">
+      <c r="A27" s="58" t="inlineStr">
         <is>
           <t>G₀ =</t>
         </is>
@@ -37307,17 +39312,17 @@
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>Episode 2</t>
         </is>
       </c>
-      <c r="B29" s="46" t="n"/>
-      <c r="C29" s="46" t="n"/>
-      <c r="D29" s="46" t="n"/>
-      <c r="E29" s="46" t="n"/>
-      <c r="F29" s="46" t="n"/>
-      <c r="G29" s="46" t="n"/>
+      <c r="B29" s="57" t="n"/>
+      <c r="C29" s="57" t="n"/>
+      <c r="D29" s="57" t="n"/>
+      <c r="E29" s="57" t="n"/>
+      <c r="F29" s="57" t="n"/>
+      <c r="G29" s="57" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -37977,7 +39982,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="47" t="inlineStr">
+      <c r="A51" s="58" t="inlineStr">
         <is>
           <t>G₀ =</t>
         </is>
@@ -37989,17 +39994,17 @@
     </row>
     <row r="52"/>
     <row r="53">
-      <c r="A53" s="45" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
         <is>
           <t>Episode 3</t>
         </is>
       </c>
-      <c r="B53" s="46" t="n"/>
-      <c r="C53" s="46" t="n"/>
-      <c r="D53" s="46" t="n"/>
-      <c r="E53" s="46" t="n"/>
-      <c r="F53" s="46" t="n"/>
-      <c r="G53" s="46" t="n"/>
+      <c r="B53" s="57" t="n"/>
+      <c r="C53" s="57" t="n"/>
+      <c r="D53" s="57" t="n"/>
+      <c r="E53" s="57" t="n"/>
+      <c r="F53" s="57" t="n"/>
+      <c r="G53" s="57" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -38659,7 +40664,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="47" t="inlineStr">
+      <c r="A75" s="58" t="inlineStr">
         <is>
           <t>G₀ =</t>
         </is>
@@ -38671,17 +40676,17 @@
     </row>
     <row r="76"/>
     <row r="77">
-      <c r="A77" s="45" t="inlineStr">
+      <c r="A77" s="56" t="inlineStr">
         <is>
           <t>Episode 4</t>
         </is>
       </c>
-      <c r="B77" s="46" t="n"/>
-      <c r="C77" s="46" t="n"/>
-      <c r="D77" s="46" t="n"/>
-      <c r="E77" s="46" t="n"/>
-      <c r="F77" s="46" t="n"/>
-      <c r="G77" s="46" t="n"/>
+      <c r="B77" s="57" t="n"/>
+      <c r="C77" s="57" t="n"/>
+      <c r="D77" s="57" t="n"/>
+      <c r="E77" s="57" t="n"/>
+      <c r="F77" s="57" t="n"/>
+      <c r="G77" s="57" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -39155,7 +41160,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="47" t="inlineStr">
+      <c r="A93" s="58" t="inlineStr">
         <is>
           <t>G₀ =</t>
         </is>
@@ -39167,17 +41172,17 @@
     </row>
     <row r="94"/>
     <row r="95">
-      <c r="A95" s="45" t="inlineStr">
+      <c r="A95" s="56" t="inlineStr">
         <is>
           <t>Episode 5</t>
         </is>
       </c>
-      <c r="B95" s="46" t="n"/>
-      <c r="C95" s="46" t="n"/>
-      <c r="D95" s="46" t="n"/>
-      <c r="E95" s="46" t="n"/>
-      <c r="F95" s="46" t="n"/>
-      <c r="G95" s="46" t="n"/>
+      <c r="B95" s="57" t="n"/>
+      <c r="C95" s="57" t="n"/>
+      <c r="D95" s="57" t="n"/>
+      <c r="E95" s="57" t="n"/>
+      <c r="F95" s="57" t="n"/>
+      <c r="G95" s="57" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -39279,7 +41284,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="47" t="inlineStr">
+      <c r="A99" s="58" t="inlineStr">
         <is>
           <t>G₀ =</t>
         </is>
@@ -39302,374 +41307,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monte Carlo — First-Visit V(s) and Q(s,a) Estimation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Each cell = G_t of the first visit in that episode (cross-sheet ref).  V/Q = AVERAGE of those returns.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>V^MC(s) = average of first-visit G_t per state</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Ep1 G_t ✱</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Ep2 G_t ✱</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Ep3 G_t ✱</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Ep4 G_t ✱</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Ep5 G_t ✱</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>V^MC(s) ✱</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Cool</t>
-        </is>
-      </c>
-      <c r="B6" s="29">
-        <f>'MC-Episodes'!G7</f>
-        <v/>
-      </c>
-      <c r="C6" s="29">
-        <f>'MC-Episodes'!G31</f>
-        <v/>
-      </c>
-      <c r="D6" s="29">
-        <f>'MC-Episodes'!G55</f>
-        <v/>
-      </c>
-      <c r="E6" s="29">
-        <f>'MC-Episodes'!G79</f>
-        <v/>
-      </c>
-      <c r="F6" s="29">
-        <f>'MC-Episodes'!G97</f>
-        <v/>
-      </c>
-      <c r="G6" s="29">
-        <f>AVERAGE(B6:F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="B7" s="29">
-        <f>'MC-Episodes'!G15</f>
-        <v/>
-      </c>
-      <c r="C7" s="29">
-        <f>'MC-Episodes'!G32</f>
-        <v/>
-      </c>
-      <c r="D7" s="29">
-        <f>'MC-Episodes'!G56</f>
-        <v/>
-      </c>
-      <c r="E7" s="29">
-        <f>'MC-Episodes'!G81</f>
-        <v/>
-      </c>
-      <c r="F7" s="29">
-        <f>'MC-Episodes'!G98</f>
-        <v/>
-      </c>
-      <c r="G7" s="29">
-        <f>AVERAGE(B7:F7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="41" t="inlineStr">
-        <is>
-          <t>Overheated</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q^MC(s,a) = average of first-visit G_t per (s,a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>(s, a)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Ep1 G_t ✱</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Ep2 G_t ✱</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Ep3 G_t ✱</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Ep4 G_t ✱</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Ep5 G_t ✱</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Q^MC(s,a) ✱</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>(Cool, Slow)</t>
-        </is>
-      </c>
-      <c r="B12" s="29">
-        <f>'MC-Episodes'!G20</f>
-        <v/>
-      </c>
-      <c r="C12" s="29">
-        <f>'MC-Episodes'!G49</f>
-        <v/>
-      </c>
-      <c r="D12" s="29">
-        <f>'MC-Episodes'!G73</f>
-        <v/>
-      </c>
-      <c r="G12" s="29">
-        <f>AVERAGE(B12:F12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>(Cool, Fast)</t>
-        </is>
-      </c>
-      <c r="B13" s="29">
-        <f>'MC-Episodes'!G7</f>
-        <v/>
-      </c>
-      <c r="C13" s="29">
-        <f>'MC-Episodes'!G31</f>
-        <v/>
-      </c>
-      <c r="D13" s="29">
-        <f>'MC-Episodes'!G55</f>
-        <v/>
-      </c>
-      <c r="E13" s="29">
-        <f>'MC-Episodes'!G79</f>
-        <v/>
-      </c>
-      <c r="F13" s="29">
-        <f>'MC-Episodes'!G97</f>
-        <v/>
-      </c>
-      <c r="G13" s="29">
-        <f>AVERAGE(B13:F13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>(Warm, Slow)</t>
-        </is>
-      </c>
-      <c r="B14" s="29">
-        <f>'MC-Episodes'!G15</f>
-        <v/>
-      </c>
-      <c r="C14" s="29">
-        <f>'MC-Episodes'!G32</f>
-        <v/>
-      </c>
-      <c r="D14" s="29">
-        <f>'MC-Episodes'!G56</f>
-        <v/>
-      </c>
-      <c r="E14" s="29">
-        <f>'MC-Episodes'!G81</f>
-        <v/>
-      </c>
-      <c r="G14" s="29">
-        <f>AVERAGE(B14:F14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>(Warm, Fast)</t>
-        </is>
-      </c>
-      <c r="D15" s="29">
-        <f>'MC-Episodes'!G74</f>
-        <v/>
-      </c>
-      <c r="E15" s="29">
-        <f>'MC-Episodes'!G92</f>
-        <v/>
-      </c>
-      <c r="F15" s="29">
-        <f>'MC-Episodes'!G98</f>
-        <v/>
-      </c>
-      <c r="G15" s="29">
-        <f>AVERAGE(B15:F15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Greedy Policy from Q^MC: π(s) = argmax_a Q^MC(s,a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>π(s) ✱</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Q^MC(s,π(s)) ✱</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Cool</t>
-        </is>
-      </c>
-      <c r="B19" s="29">
-        <f>IF(G13&gt;=G12,"Fast","Slow")</f>
-        <v/>
-      </c>
-      <c r="C19" s="29">
-        <f>MAX(G12,G13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Warm</t>
-        </is>
-      </c>
-      <c r="B20" s="29">
-        <f>IF(G15&gt;=G14,"Fast","Slow")</f>
-        <v/>
-      </c>
-      <c r="C20" s="29">
-        <f>MAX(G14,G15)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>